--- a/data/Branch-Shift-Roster-Nov2026.xlsx
+++ b/data/Branch-Shift-Roster-Nov2026.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T63"/>
+  <dimension ref="A1:T66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -556,27 +556,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E1001</t>
+          <t>CT1028</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Farah binti Hassan</t>
+          <t>Juan Dunlap</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Ipoh</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Teller</t>
+          <t>Branch Supervisor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -631,17 +631,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -649,36 +649,32 @@
           <t>AM</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Annual leave 9-10 Nov</t>
-        </is>
-      </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E1002</t>
+          <t>CT1017</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Ibrahim</t>
+          <t>David Ford</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Branch Manager</t>
+          <t>Risk Analyst</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -688,12 +684,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -708,12 +704,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,17 +724,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -748,45 +744,49 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>MC 12-13 Nov</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E1003</t>
+          <t>CT1032</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wong Lee</t>
+          <t>Dr. Jordan Rodriguez</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Kota Kinabalu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Risk Analyst</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -811,27 +811,27 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -846,65 +846,69 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>MC 12-13 Nov</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E1004</t>
+          <t>CT1023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kamal Nair</t>
+          <t>Justin Baker</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>JB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Branch Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -914,7 +918,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -924,12 +928,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -939,7 +943,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -952,12 +956,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E1005</t>
+          <t>CT1050</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Farah Subramaniam</t>
+          <t>Jessica Owens</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -967,37 +971,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Risk Analyst</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1007,12 +1011,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1027,17 +1031,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1045,21 +1049,17 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Annual leave 9-10 Nov</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E1006</t>
+          <t>CT1073</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Farah Ahmad</t>
+          <t>Kimberly Turner</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Teller</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1094,37 +1094,37 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1152,22 +1152,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E1007</t>
+          <t>CT1011</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wong Bin Abdullah</t>
+          <t>Lori Mcclure</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Kota Kinabalu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>Senior Auditor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1242,34 +1242,30 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Mat leave returnee</t>
-        </is>
-      </c>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E1008</t>
+          <t>CT1096</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ismail Nair</t>
+          <t>Todd Wilson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>Audit Manager</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1279,17 +1275,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1299,17 +1295,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1324,12 +1320,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1339,7 +1335,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1349,44 +1345,44 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Annual leave 9-10 Nov</t>
+          <t>Hospitalisation leave</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E1009</t>
+          <t>CT1018</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ravi Nair</t>
+          <t>Margaret Hawkins DDS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Ipoh</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Teller</t>
+          <t>Compliance Officer</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1401,27 +1397,27 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1441,69 +1437,65 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>On AML training Wk2</t>
-        </is>
-      </c>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E1010</t>
+          <t>CT1115</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hafiz Ibrahim</t>
+          <t>Jennifer Soto</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Ipoh</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Teller</t>
+          <t>Senior Finance Exec</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1518,17 +1510,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1538,7 +1530,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1548,80 +1540,84 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>On AML training Wk2</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E1011</t>
+          <t>CT1043</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ismail Ahmad</t>
+          <t>Jesse Wright</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Kota Kinabalu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Branch Manager</t>
+          <t>CS Team Lead</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1631,7 +1627,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1641,35 +1637,39 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Annual leave 9-10 Nov</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E1012</t>
+          <t>CT1097</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wei Lun Ibrahim</t>
+          <t>Victor Baker</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Subang</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Branch Manager</t>
+          <t>Head of HR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1752,22 +1752,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E1013</t>
+          <t>CT1065</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Siti Nair</t>
+          <t>Stefanie Sanchez</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Kota Kinabalu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Teller</t>
+          <t>Risk Manager</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1822,17 +1822,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1845,46 +1845,42 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>On AML training Wk2</t>
-        </is>
-      </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E1014</t>
+          <t>CT1085</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wong Subramaniam</t>
+          <t>Mr. Hunter Fleming</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Risk Manager</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1894,7 +1890,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1909,7 +1905,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1929,12 +1925,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1947,36 +1943,32 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>On AML training Wk2</t>
-        </is>
-      </c>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E1015</t>
+          <t>CT1068</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Priya Ng</t>
+          <t>Deborah Anderson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>Senior CS Executive</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1991,7 +1983,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2001,7 +1993,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2016,22 +2008,22 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2041,85 +2033,89 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>MC 12-13 Nov</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E1016</t>
+          <t>CT1069</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nurul Subramaniam</t>
+          <t>Eugene Walton</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KL HQ</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Branch Manager</t>
+          <t>Head of Treasury</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2129,7 +2125,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2139,29 +2135,25 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Mat leave returnee</t>
-        </is>
-      </c>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E1017</t>
+          <t>CT1003</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lim Wong</t>
+          <t>Jennifer Johnson</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2171,17 +2163,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>AML Analyst</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2191,22 +2183,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2221,32 +2213,32 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2258,12 +2250,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E1018</t>
+          <t>CT1054</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Priya Ibrahim</t>
+          <t>Danielle Leblanc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2273,7 +2265,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2293,17 +2285,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2318,7 +2310,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2328,7 +2320,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2338,12 +2330,12 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2353,39 +2345,39 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>On AML training Wk2</t>
+          <t>Mat leave returnee</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E1019</t>
+          <t>CT1094</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Devi Bin Abdullah</t>
+          <t>Garrett Lin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Subang</t>
+          <t>Kota Kinabalu</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Teller</t>
+          <t>CS Team Lead</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2395,12 +2387,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2415,27 +2407,27 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2453,21 +2445,17 @@
           <t>AM</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Hospitalisation leave</t>
-        </is>
-      </c>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E1020</t>
+          <t>CT1076</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ismail Nair</t>
+          <t>Ashley Tran</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2477,12 +2465,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Senior Compliance Officer</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2497,22 +2485,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2532,17 +2520,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2555,17 +2543,21 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Hospitalisation leave</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E1021</t>
+          <t>CT1040</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ravi Bin Abdullah</t>
+          <t>Kelsey Obrien</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2575,7 +2567,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Head of Treasury</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2595,7 +2587,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2610,7 +2602,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2620,12 +2612,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2635,49 +2627,45 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>On AML training Wk2</t>
-        </is>
-      </c>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E1022</t>
+          <t>CT1010</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Siti Subramaniam</t>
+          <t>William Gray</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Subang</t>
+          <t>Kota Kinabalu</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Finance Executive</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2692,12 +2680,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2712,22 +2700,22 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2742,7 +2730,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2752,59 +2740,59 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Annual leave 9-10 Nov</t>
+          <t>Mat leave returnee</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E1023</t>
+          <t>CT1053</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Farah Tan</t>
+          <t>Joshua Taylor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Subang</t>
+          <t>JB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>HR Business Partner</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2819,22 +2807,22 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2844,12 +2832,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2862,22 +2850,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E1024</t>
+          <t>CT1049</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Siti Ibrahim</t>
+          <t>Jennifer Davis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Subang</t>
+          <t>Ipoh</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>Branch Manager</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2902,12 +2890,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2917,7 +2905,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2927,7 +2915,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2937,7 +2925,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2955,81 +2943,77 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>On AML training Wk2</t>
-        </is>
-      </c>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E1025</t>
+          <t>CT1109</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wong Ibrahim</t>
+          <t>Julie Ramos</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Subang</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Teller</t>
+          <t>HR Business Partner</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3044,49 +3028,49 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Annual leave 9-10 Nov</t>
+          <t>On AML training Wk2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E1026</t>
+          <t>CT1064</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kamal Tan</t>
+          <t>Barry Hensley</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Subang</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>Senior Teller</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3101,7 +3085,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3111,27 +3095,27 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3151,12 +3135,12 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3164,37 +3148,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E1027</t>
+          <t>CT1088</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aiman Tan</t>
+          <t>Rita Keith MD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Subang</t>
+          <t>JB</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>Risk Analyst</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3204,27 +3188,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3257,31 +3241,27 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>On AML training Wk2</t>
-        </is>
-      </c>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E1028</t>
+          <t>CT1034</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aiman Tan</t>
+          <t>Candice Ashley</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Subang</t>
+          <t>KL HQ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Branch Manager</t>
+          <t>Head of Treasury</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3291,7 +3271,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3306,7 +3286,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3316,27 +3296,27 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3346,12 +3326,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3364,27 +3344,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>E1029</t>
+          <t>CT1075</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Siti Tan</t>
+          <t>Ashley Humphrey</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>Subang</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Branch Manager</t>
+          <t>Senior CS Executive</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3394,22 +3374,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3419,7 +3399,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3429,22 +3409,22 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3457,37 +3437,41 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>On AML training Wk2</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>E1030</t>
+          <t>CT1083</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ismail Tan</t>
+          <t>Sandra Aguilar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>KL HQ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>FX Dealer</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3497,7 +3481,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3507,17 +3491,17 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3537,7 +3521,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3547,7 +3531,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3557,29 +3541,29 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Annual leave 9-10 Nov</t>
+          <t>Mat leave returnee</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>E1031</t>
+          <t>CT1079</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Priya Nair</t>
+          <t>Madison Calderon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>KL HQ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Senior CS Executive</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3594,22 +3578,22 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3619,80 +3603,84 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Annual leave 9-10 Nov</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>E1032</t>
+          <t>CT1091</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hafiz Tan</t>
+          <t>James Williams</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>Kota Kinabalu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Branch Manager</t>
+          <t>Branch Supervisor</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3702,17 +3690,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3722,7 +3710,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3737,17 +3725,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3755,31 +3743,27 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Mat leave returnee</t>
-        </is>
-      </c>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>E1033</t>
+          <t>CT1058</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lim Tan</t>
+          <t>April Myers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>Kota Kinabalu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3789,22 +3773,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3819,7 +3803,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3834,22 +3818,22 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3857,17 +3841,21 @@
           <t>AM</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Annual leave 9-10 Nov</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>E1034</t>
+          <t>CT1095</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kamal Subramaniam</t>
+          <t>Margaret Ross</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3877,7 +3865,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Senior Compliance Officer</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3892,17 +3880,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3912,17 +3900,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3932,74 +3920,70 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Mat leave returnee</t>
-        </is>
-      </c>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>E1035</t>
+          <t>CT1024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lim Wong</t>
+          <t>Lauren Cox</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>JB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>CS Team Lead</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4014,7 +3998,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4029,7 +4013,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -4039,7 +4023,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -4057,17 +4041,21 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Annual leave 9-10 Nov</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>E1036</t>
+          <t>CT1039</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aiman Ahmad</t>
+          <t>Beth Keller</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4077,22 +4065,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>FX Dealer</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4102,27 +4090,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4132,12 +4120,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -4160,22 +4148,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>E1037</t>
+          <t>CT1012</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ismail Lee</t>
+          <t>Michael Williams</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Penang</t>
+          <t>Ipoh</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Teller</t>
+          <t>Compliance Officer</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4185,7 +4173,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4195,22 +4183,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4220,12 +4208,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4240,55 +4228,59 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Hospitalisation leave</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>E1038</t>
+          <t>CT1055</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aiman Subramaniam</t>
+          <t>Scott Garcia</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JB</t>
+          <t>Kota Kinabalu</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>AML Analyst</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4298,12 +4290,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4313,12 +4305,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4328,22 +4320,22 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4351,37 +4343,41 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>On AML training Wk2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>E1039</t>
+          <t>CT1099</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kamal Bin Abdullah</t>
+          <t>Kayla Cruz</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JB</t>
+          <t>KL HQ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Teller</t>
+          <t>Senior Auditor</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4391,7 +4387,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4401,22 +4397,22 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4431,12 +4427,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4446,59 +4442,59 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Mat leave returnee</t>
+          <t>On AML training Wk2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>E1040</t>
+          <t>CT1113</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Farah Ibrahim</t>
+          <t>Courtney Gonzalez</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JB</t>
+          <t>Subang</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Branch Manager</t>
+          <t>CS Team Lead</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4508,22 +4504,22 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4533,17 +4529,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4556,72 +4552,72 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>E1041</t>
+          <t>CT1063</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nurul Nair</t>
+          <t>Tonya Miller</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JB</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Head of Treasury</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4636,45 +4632,49 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Hospitalisation leave</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>E1042</t>
+          <t>CT1008</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hafiz Subramaniam</t>
+          <t>Brandon Davis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JB</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Finance Executive</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4744,34 +4744,30 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Mat leave returnee</t>
-        </is>
-      </c>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>E1043</t>
+          <t>CT1052</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lim Ibrahim</t>
+          <t>Gerald Hensley</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JB</t>
+          <t>KL HQ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Senior CS Executive</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4781,12 +4777,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4796,47 +4792,47 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4846,69 +4842,65 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Hospitalisation leave</t>
-        </is>
-      </c>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>E1044</t>
+          <t>CT1066</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hafiz Wong</t>
+          <t>Angela Sandoval</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JB</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Risk Manager</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4918,12 +4910,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4938,40 +4930,44 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>On AML training Wk2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>E1045</t>
+          <t>CT1059</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wong Wong</t>
+          <t>Dustin Horton</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JB</t>
+          <t>Kota Kinabalu</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4981,7 +4977,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5001,7 +4997,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5011,7 +5007,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5021,12 +5017,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5046,7 +5042,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -5058,12 +5054,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>E1046</t>
+          <t>CT1119</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Devi Nair</t>
+          <t>Joseph Williams</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5073,7 +5069,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>HR Executive</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5088,27 +5084,27 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5118,7 +5114,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5128,54 +5124,54 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>Hospitalisation leave</t>
+          <t>Mat leave returnee</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>E1047</t>
+          <t>CT1044</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Devi binti Hassan</t>
+          <t>Leah Hall</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kota Kinabalu</t>
+          <t>Subang</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>HR Business Partner</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5185,7 +5181,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5200,7 +5196,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5215,7 +5211,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5230,7 +5226,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5240,17 +5236,17 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5258,12 +5254,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>E1048</t>
+          <t>CT1004</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tan Lee</t>
+          <t>Lindsay Hoffman</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5273,7 +5269,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>Auditor</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5283,17 +5279,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5303,7 +5299,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5313,37 +5309,37 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5356,42 +5352,42 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>E1049</t>
+          <t>CT1103</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kamal binti Hassan</t>
+          <t>Lisa Alvarado</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kota Kinabalu</t>
+          <t>Kuching</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>FX Dealer</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5401,32 +5397,32 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5446,30 +5442,34 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Mat leave returnee</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>E1050</t>
+          <t>CT1070</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Farah Subramaniam</t>
+          <t>Marc Hart</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kota Kinabalu</t>
+          <t>KL HQ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Teller</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5499,17 +5499,17 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5519,22 +5519,22 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5547,36 +5547,32 @@
           <t>AM</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Hospitalisation leave</t>
-        </is>
-      </c>
+      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>E1051</t>
+          <t>CT1071</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Siti Ibrahim</t>
+          <t>Christy Baker</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kota Kinabalu</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>AML Analyst</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5586,17 +5582,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5606,37 +5602,37 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5651,19 +5647,19 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Annual leave 9-10 Nov</t>
+          <t>On AML training Wk2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>E1052</t>
+          <t>CT1038</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kamal Ibrahim</t>
+          <t>John Jones</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5673,7 +5669,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5688,62 +5684,62 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -5751,17 +5747,21 @@
           <t>PM</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Annual leave 9-10 Nov</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>E1053</t>
+          <t>CT1025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ismail binti Hassan</t>
+          <t>Ann Williams</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Senior Teller</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5781,22 +5781,22 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5826,54 +5826,50 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Mat leave returnee</t>
-        </is>
-      </c>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>E1054</t>
+          <t>CT1041</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Priya Tan</t>
+          <t>Nicole Vaughn</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>KL HQ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Compliance Officer</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5883,7 +5879,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5893,17 +5889,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5918,12 +5914,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5933,17 +5929,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -5953,34 +5949,34 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>On AML training Wk2</t>
+          <t>MC 12-13 Nov</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>E1055</t>
+          <t>CT1042</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wong Subramaniam</t>
+          <t>Zachary Santos</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Senior Teller</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5995,7 +5991,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6010,7 +6006,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6020,12 +6016,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -6035,49 +6031,49 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Mat leave returnee</t>
+          <t>MC 12-13 Nov</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>E1056</t>
+          <t>CT1090</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ravi Ibrahim</t>
+          <t>Robert Adams</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>Kota Kinabalu</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Branch Compliance</t>
+          <t>Branch Supervisor</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6092,37 +6088,37 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6132,59 +6128,55 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Hospitalisation leave</t>
-        </is>
-      </c>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E1057</t>
+          <t>CT1020</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Siti Ibrahim</t>
+          <t>Debra Clark</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kuching</t>
+          <t>Penang</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>Audit Manager</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6194,27 +6186,27 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6229,7 +6221,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -6239,49 +6231,45 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Hospitalisation leave</t>
-        </is>
-      </c>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>E1058</t>
+          <t>CT1120</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Priya Tan</t>
+          <t>Bryan Anderson</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ipoh</t>
+          <t>Subang</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6291,7 +6279,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6301,7 +6289,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6316,7 +6304,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6326,70 +6314,74 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr"/>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>On AML training Wk2</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E1059</t>
+          <t>CT1098</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nurul binti Hassan</t>
+          <t>Gregory Hartman</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ipoh</t>
+          <t>KL HQ</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Teller</t>
+          <t>CS Team Lead</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6404,12 +6396,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6419,27 +6411,27 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -6449,40 +6441,44 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr"/>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Mat leave returnee</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>E1060</t>
+          <t>CT1026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tan Bin Abdullah</t>
+          <t>Christopher Becker</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ipoh</t>
+          <t>KL HQ</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sr Teller</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6497,7 +6493,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6512,47 +6508,47 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -6564,22 +6560,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>E1061</t>
+          <t>CT1062</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wong Ibrahim</t>
+          <t>Karen Calhoun</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ipoh</t>
+          <t>JB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Customer Service</t>
+          <t>Teller</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6594,12 +6590,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6609,12 +6605,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6624,7 +6620,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6634,27 +6630,27 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6662,100 +6658,402 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>E1062</t>
+          <t>CT1009</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Priya Ahmad</t>
+          <t>Deborah Williams</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>Kota Kinabalu</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Head of Compliance</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>MC 12-13 Nov</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CT1036</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Shawn Decker</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Kota Kinabalu</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Senior CS Executive</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CT1061</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Joshua Adkins</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Kuching</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Finance Executive</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CT1007</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Gerald Moore</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>Ipoh</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Teller</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CS Executive</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Mat leave returnee</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6768,11 +7066,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6831,7 +7129,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>≥1 full day off per 7-day cycle</t>
+          <t>≥1 full day off per 7-day cycle (Employment Act)</t>
         </is>
       </c>
     </row>
@@ -6856,6 +7154,18 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>Last 3 working days of month (payroll/STR cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cross-branch cover</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Branch Manager may not approve own swap; needs Head of Ops sign-off</t>
         </is>
       </c>
     </row>
